--- a/src/main/resources/espacios/1 Step/1 - Both, Neither.xlsx
+++ b/src/main/resources/espacios/1 Step/1 - Both, Neither.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="271">
   <si>
     <t xml:space="preserve">On Both</t>
   </si>
@@ -39,16 +39,19 @@
     <t xml:space="preserve">ɑː juː əˈveɪləbᵊl fɔːr ə ˈmiːtɪŋ ɒn bəʊθ ˈfraɪdeɪ ænd ˈsætədeɪ?</t>
   </si>
   <si>
+    <t xml:space="preserve">HEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Are you free to meet on both Friday and Saturday?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">¿Puedes reunirte tanto el viernes como el sábado?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ɑː juː friː tuː miːt ɒn bəʊθ ˈfraɪdeɪ ænd ˈsætədeɪ?</t>
+  </si>
+  <si>
     <t xml:space="preserve">EXAMPLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Are you free to meet on both Friday and Saturday?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">¿Puedes reunirte tanto el viernes como el sábado?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ɑː juː friː tuː miːt ɒn bəʊθ ˈfraɪdeɪ ænd ˈsætədeɪ?</t>
   </si>
   <si>
     <t xml:space="preserve">Can we meet on both Friday and Saturday?</t>
@@ -1105,116 +1108,116 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>5</v>
@@ -1222,654 +1225,660 @@
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1901,223 +1910,223 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F2" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -2146,224 +2155,224 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F1" s="5"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="F2" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
